--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9F0764F-945F-4FAD-89C7-08FE1F72FF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{592D6B02-DCD0-44CA-8052-3F8317CD1D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>FieldName</t>
   </si>
@@ -60,7 +60,7 @@
     <t>VHM</t>
   </si>
   <si>
-    <t>yes</t>
+    <t>No</t>
   </si>
   <si>
     <t>Customer Name</t>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>International Address</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -169,12 +166,12 @@
     <t>Ecatering Business Unit</t>
   </si>
   <si>
+    <t>Social</t>
+  </si>
+  <si>
     <t>Business Units</t>
   </si>
   <si>
-    <t>Social</t>
-  </si>
-  <si>
     <t>Tax ID</t>
   </si>
   <si>
@@ -185,6 +182,9 @@
   </si>
   <si>
     <t>Mailing List</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
   <si>
     <t>Referral Type</t>
@@ -660,36 +660,36 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
         <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -697,23 +697,23 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
         <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
         <v>28</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>12345</v>
@@ -721,12 +721,12 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>96323456</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -742,7 +742,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>111</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>11</v>
@@ -774,15 +774,15 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
         <v>38</v>
-      </c>
-      <c r="B26" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>111</v>
@@ -790,15 +790,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="3">
         <v>46043</v>
@@ -814,6 +814,9 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -822,12 +825,12 @@
         <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -835,7 +838,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34">
         <v>12</v>
@@ -843,7 +846,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35">
         <v>11</v>
@@ -851,10 +854,10 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
         <v>50</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -870,7 +873,7 @@
         <v>53</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{592D6B02-DCD0-44CA-8052-3F8317CD1D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E16355-D8E2-4CED-86BD-EF89FCBCE016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="86">
   <si>
     <t>FieldName</t>
   </si>
@@ -194,13 +195,109 @@
   </si>
   <si>
     <t>Tax Exempt</t>
+  </si>
+  <si>
+    <t>Business Unit</t>
+  </si>
+  <si>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>Event Type</t>
+  </si>
+  <si>
+    <t>First Call Time</t>
+  </si>
+  <si>
+    <t>Revenue Stream</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Begin Time</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Billing Customer</t>
+  </si>
+  <si>
+    <t>Platter Type</t>
+  </si>
+  <si>
+    <t>Account Executive</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Event Name</t>
+  </si>
+  <si>
+    <t>wedding</t>
+  </si>
+  <si>
+    <t>Proposal Status</t>
+  </si>
+  <si>
+    <t>Event Theme</t>
+  </si>
+  <si>
+    <t>Adult Count</t>
+  </si>
+  <si>
+    <t>Staff Count</t>
+  </si>
+  <si>
+    <t>Estimated $/Person</t>
+  </si>
+  <si>
+    <t>Band Count</t>
+  </si>
+  <si>
+    <t>Kids Count</t>
+  </si>
+  <si>
+    <t>Misc Count</t>
+  </si>
+  <si>
+    <t>Contact Name</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>test name</t>
+  </si>
+  <si>
+    <t>Work Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>Home Phone</t>
+  </si>
+  <si>
+    <t>test naame</t>
+  </si>
+  <si>
+    <t>test comments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +327,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="AvenirLTStd-Roman"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -248,10 +360,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -260,8 +373,11 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -879,4 +995,300 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E467A122-BD15-44D1-83AE-AD244E894C1D}">
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>98765432</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36">
+        <v>456776543456</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38">
+        <v>876543456</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{302D5C3D-84DC-4D64-9AFA-1CFBD5C0221C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E16355-D8E2-4CED-86BD-EF89FCBCE016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF2BCCFA-3D19-46EB-9E29-09529709445F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="102">
   <si>
     <t>FieldName</t>
   </si>
@@ -197,31 +197,46 @@
     <t>Tax Exempt</t>
   </si>
   <si>
-    <t>Business Unit</t>
-  </si>
-  <si>
-    <t>Event Manager</t>
+    <t xml:space="preserve">Business Unit </t>
+  </si>
+  <si>
+    <t>Will Call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Manager </t>
+  </si>
+  <si>
+    <t>Aarevalo , Yudi</t>
   </si>
   <si>
     <t>Event Type</t>
   </si>
   <si>
-    <t>First Call Time</t>
+    <t>Buffet Lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Call Time </t>
   </si>
   <si>
     <t>Revenue Stream</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Begin Time</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>County</t>
+    <t xml:space="preserve">Customer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begin Time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status </t>
+  </si>
+  <si>
+    <t>abcd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County </t>
+  </si>
+  <si>
+    <t>Taiwan</t>
   </si>
   <si>
     <t>Billing Customer</t>
@@ -230,9 +245,15 @@
     <t>Platter Type</t>
   </si>
   <si>
+    <t>equipment</t>
+  </si>
+  <si>
     <t>Account Executive</t>
   </si>
   <si>
+    <t>sam</t>
+  </si>
+  <si>
     <t>End Time</t>
   </si>
   <si>
@@ -245,16 +266,19 @@
     <t>Proposal Status</t>
   </si>
   <si>
-    <t>Event Theme</t>
+    <t>New</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Theme </t>
   </si>
   <si>
     <t>Adult Count</t>
   </si>
   <si>
-    <t>Staff Count</t>
-  </si>
-  <si>
-    <t>Estimated $/Person</t>
+    <t xml:space="preserve">Staff Count </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated $/Person </t>
   </si>
   <si>
     <t>Band Count</t>
@@ -263,22 +287,40 @@
     <t>Kids Count</t>
   </si>
   <si>
-    <t>Misc Count</t>
+    <t xml:space="preserve">Misc Count </t>
   </si>
   <si>
     <t>Contact Name</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>test name</t>
-  </si>
-  <si>
-    <t>Work Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
+    <t xml:space="preserve">Zip </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">State </t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t>test John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Phone </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email </t>
   </si>
   <si>
     <t>test@gmail.com</t>
@@ -287,7 +329,13 @@
     <t>Home Phone</t>
   </si>
   <si>
+    <t xml:space="preserve">Fax </t>
+  </si>
+  <si>
     <t>test naame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments </t>
   </si>
   <si>
     <t>test comments</t>
@@ -297,7 +345,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,13 +383,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="AvenirLTStd-Roman"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -364,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -373,7 +414,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -999,34 +1039,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E467A122-BD15-44D1-83AE-AD244E894C1D}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A2:B42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1036,70 +1077,88 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>78</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1112,7 +1171,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1120,7 +1179,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -1128,7 +1187,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1136,7 +1195,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1144,7 +1203,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -1152,7 +1211,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -1160,12 +1219,12 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="B27">
         <v>12345</v>
@@ -1173,15 +1232,15 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="6" t="s">
-        <v>33</v>
+      <c r="A29" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -1189,7 +1248,10 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1215,7 +1277,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
@@ -1223,15 +1285,15 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B36">
         <v>456776543456</v>
@@ -1239,15 +1301,15 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B38">
         <v>876543456</v>
@@ -1255,26 +1317,26 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="B39">
         <v>12345</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>78</v>
+      <c r="A40" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:2">

--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF2BCCFA-3D19-46EB-9E29-09529709445F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
   <si>
     <t>FieldName</t>
   </si>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -476,7 +476,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -528,7 +528,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -722,14 +722,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -811,7 +811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30.75">
+    <row r="11" spans="1:6" ht="30">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1038,14 +1038,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E467A122-BD15-44D1-83AE-AD244E894C1D}">
-  <dimension ref="A2:B42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>54</v>
@@ -1349,8 +1357,314 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B37" r:id="rId1" xr:uid="{302D5C3D-84DC-4D64-9AFA-1CFBD5C0221C}"/>
+    <hyperlink ref="B37" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="16.140625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20">
+        <v>96323456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B00106F-47E4-4379-BFD3-6BA9E709ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="96">
   <si>
     <t>FieldName</t>
   </si>
@@ -197,63 +198,66 @@
     <t>Tax Exempt</t>
   </si>
   <si>
-    <t xml:space="preserve">Business Unit </t>
+    <t>Business Unit</t>
   </si>
   <si>
     <t>Will Call</t>
   </si>
   <si>
-    <t xml:space="preserve">Event Manager </t>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>Alejos , Diana</t>
+  </si>
+  <si>
+    <t>Event Type</t>
+  </si>
+  <si>
+    <t>Buffet Lunch</t>
+  </si>
+  <si>
+    <t>Platter Type</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>First Call Time</t>
+  </si>
+  <si>
+    <t>Revenue Stream</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>360 Live Media</t>
+  </si>
+  <si>
+    <t>Begin Time</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>abcd</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>Billing Customer</t>
+  </si>
+  <si>
+    <t>Account Executive</t>
   </si>
   <si>
     <t>Aarevalo , Yudi</t>
   </si>
   <si>
-    <t>Event Type</t>
-  </si>
-  <si>
-    <t>Buffet Lunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Call Time </t>
-  </si>
-  <si>
-    <t>Revenue Stream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Begin Time </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status </t>
-  </si>
-  <si>
-    <t>abcd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">County </t>
-  </si>
-  <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
-    <t>Billing Customer</t>
-  </si>
-  <si>
-    <t>Platter Type</t>
-  </si>
-  <si>
-    <t>equipment</t>
-  </si>
-  <si>
-    <t>Account Executive</t>
-  </si>
-  <si>
-    <t>sam</t>
-  </si>
-  <si>
     <t>End Time</t>
   </si>
   <si>
@@ -269,16 +273,16 @@
     <t>New</t>
   </si>
   <si>
-    <t xml:space="preserve">Event Theme </t>
+    <t>Event Theme</t>
   </si>
   <si>
     <t>Adult Count</t>
   </si>
   <si>
-    <t xml:space="preserve">Staff Count </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimated $/Person </t>
+    <t>Staff Count</t>
+  </si>
+  <si>
+    <t>Estimated $/Person</t>
   </si>
   <si>
     <t>Band Count</t>
@@ -287,55 +291,34 @@
     <t>Kids Count</t>
   </si>
   <si>
-    <t xml:space="preserve">Misc Count </t>
+    <t>Misc Count</t>
   </si>
   <si>
     <t>Contact Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Zip </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suite </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">State </t>
+    <t>test contact</t>
   </si>
   <si>
     <t>VA</t>
   </si>
   <si>
-    <t xml:space="preserve">City </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name </t>
+    <t>Name</t>
   </si>
   <si>
     <t>test John</t>
   </si>
   <si>
-    <t xml:space="preserve">Work Phone </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email </t>
+    <t>Work Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
   <si>
     <t>test@gmail.com</t>
   </si>
   <si>
     <t>Home Phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax </t>
-  </si>
-  <si>
-    <t>test naame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comments </t>
   </si>
   <si>
     <t>test comments</t>
@@ -344,8 +327,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +366,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -405,7 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -415,6 +404,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -476,7 +467,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -528,7 +519,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -722,14 +713,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1038,7 +1029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1055,7 +1046,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
       <c r="B2" t="s">
@@ -1080,93 +1071,101 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>63</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>73</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1179,7 +1178,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -1187,7 +1186,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -1195,7 +1194,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -1203,7 +1202,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -1211,7 +1210,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -1219,7 +1218,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -1227,12 +1226,15 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>12345</v>
@@ -1240,7 +1242,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1248,7 +1250,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -1256,10 +1258,10 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1285,7 +1287,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
         <v>26</v>
@@ -1293,15 +1295,15 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B36">
         <v>456776543456</v>
@@ -1309,15 +1311,15 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B38">
         <v>876543456</v>
@@ -1325,26 +1327,26 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="B39">
         <v>12345</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
-        <v>92</v>
+      <c r="A40" t="s">
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1357,14 +1359,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B37" r:id="rId1"/>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="16.140625" defaultRowHeight="15"/>
   <sheetData>

--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B00106F-47E4-4379-BFD3-6BA9E709ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31147E4C-500D-4C13-85F4-02012DC9F7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="100">
   <si>
     <t>FieldName</t>
   </si>
@@ -237,6 +237,9 @@
     <t>Begin Time</t>
   </si>
   <si>
+    <t>7/15/2026  10:15: PM</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -261,6 +264,9 @@
     <t>End Time</t>
   </si>
   <si>
+    <t>7/15/2026  11:15: PM</t>
+  </si>
+  <si>
     <t>Event Name</t>
   </si>
   <si>
@@ -303,25 +309,31 @@
     <t>VA</t>
   </si>
   <si>
+    <t>Location Information_Name</t>
+  </si>
+  <si>
+    <t>test John</t>
+  </si>
+  <si>
+    <t>Work Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>Home Phone</t>
+  </si>
+  <si>
+    <t>Contact Information_Name</t>
+  </si>
+  <si>
+    <t>test comments</t>
+  </si>
+  <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>test John</t>
-  </si>
-  <si>
-    <t>Work Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>test@gmail.com</t>
-  </si>
-  <si>
-    <t>Home Phone</t>
-  </si>
-  <si>
-    <t>test comments</t>
   </si>
 </sst>
 </file>
@@ -1030,11 +1042,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="51.5703125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1099,27 +1111,29 @@
       <c r="A9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1132,37 +1146,39 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="8"/>
+        <v>75</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>44</v>
@@ -1173,63 +1189,63 @@
         <v>47</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1245,7 +1261,7 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1253,7 +1269,7 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1261,7 +1277,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1295,15 +1311,15 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B36">
         <v>456776543456</v>
@@ -1311,15 +1327,15 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B38">
         <v>876543456</v>
@@ -1335,10 +1351,10 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1346,7 +1362,7 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1355,6 +1371,14 @@
       </c>
       <c r="B42">
         <v>212</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31147E4C-500D-4C13-85F4-02012DC9F7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8FEB768-E3F2-41AF-B5AB-096944049A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="BtsEvent" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="118">
   <si>
     <t>FieldName</t>
   </si>
@@ -201,139 +203,193 @@
     <t>Business Unit</t>
   </si>
   <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>donglee</t>
+  </si>
+  <si>
+    <t>Event Type</t>
+  </si>
+  <si>
+    <t>Bar Only</t>
+  </si>
+  <si>
+    <t>Platter Type</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>First Call Time</t>
+  </si>
+  <si>
+    <t>Revenue Stream</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>sofiya1</t>
+  </si>
+  <si>
+    <t>Begin Time</t>
+  </si>
+  <si>
+    <t>8/15/2026  10:15: AM</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Definite</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Duarty</t>
+  </si>
+  <si>
+    <t>Billing Customer</t>
+  </si>
+  <si>
+    <t>Drop-off with pick-up</t>
+  </si>
+  <si>
+    <t>Account Executive</t>
+  </si>
+  <si>
+    <t>s,sk1</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>8/15/2026  11:15: AM</t>
+  </si>
+  <si>
+    <t>Event Name</t>
+  </si>
+  <si>
+    <t>Wedding</t>
+  </si>
+  <si>
+    <t>Proposal Status</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>Event Theme</t>
+  </si>
+  <si>
+    <t>Tasting</t>
+  </si>
+  <si>
+    <t>Adult Count</t>
+  </si>
+  <si>
+    <t>Staff Count</t>
+  </si>
+  <si>
+    <t>Estimated $/Person</t>
+  </si>
+  <si>
+    <t>Band Count</t>
+  </si>
+  <si>
+    <t>Kids Count</t>
+  </si>
+  <si>
+    <t>Misc Count</t>
+  </si>
+  <si>
+    <t>Contact Name</t>
+  </si>
+  <si>
+    <t>121 Wacker</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>white street</t>
+  </si>
+  <si>
+    <t>Location Information_Name</t>
+  </si>
+  <si>
+    <t>Work Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>apparao@gmail.com</t>
+  </si>
+  <si>
+    <t>Home Phone</t>
+  </si>
+  <si>
+    <t>Contact Information_Name</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Will Call</t>
   </si>
   <si>
-    <t>Event Manager</t>
-  </si>
-  <si>
     <t>Alejos , Diana</t>
   </si>
   <si>
-    <t>Event Type</t>
-  </si>
-  <si>
     <t>Buffet Lunch</t>
   </si>
   <si>
-    <t>Platter Type</t>
-  </si>
-  <si>
     <t>equipment</t>
   </si>
   <si>
-    <t>First Call Time</t>
-  </si>
-  <si>
-    <t>Revenue Stream</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
     <t>360 Live Media</t>
   </si>
   <si>
-    <t>Begin Time</t>
-  </si>
-  <si>
     <t>7/15/2026  10:15: PM</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>abcd</t>
   </si>
   <si>
-    <t>County</t>
-  </si>
-  <si>
     <t>Taiwan</t>
   </si>
   <si>
-    <t>Billing Customer</t>
-  </si>
-  <si>
-    <t>Account Executive</t>
-  </si>
-  <si>
     <t>Aarevalo , Yudi</t>
   </si>
   <si>
-    <t>End Time</t>
-  </si>
-  <si>
     <t>7/15/2026  11:15: PM</t>
   </si>
   <si>
-    <t>Event Name</t>
-  </si>
-  <si>
     <t>wedding</t>
   </si>
   <si>
-    <t>Proposal Status</t>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
-    <t>Event Theme</t>
-  </si>
-  <si>
-    <t>Adult Count</t>
-  </si>
-  <si>
-    <t>Staff Count</t>
-  </si>
-  <si>
-    <t>Estimated $/Person</t>
-  </si>
-  <si>
-    <t>Band Count</t>
-  </si>
-  <si>
-    <t>Kids Count</t>
-  </si>
-  <si>
-    <t>Misc Count</t>
-  </si>
-  <si>
-    <t>Contact Name</t>
-  </si>
-  <si>
     <t>test contact</t>
   </si>
   <si>
     <t>VA</t>
   </si>
   <si>
-    <t>Location Information_Name</t>
-  </si>
-  <si>
     <t>test John</t>
   </si>
   <si>
-    <t>Work Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>test@gmail.com</t>
   </si>
   <si>
-    <t>Home Phone</t>
-  </si>
-  <si>
-    <t>Contact Information_Name</t>
-  </si>
-  <si>
     <t>test comments</t>
-  </si>
-  <si>
-    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1109,7 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1111,7 +1167,7 @@
       <c r="A9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1141,159 +1197,144 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>47</v>
       </c>
-      <c r="B19">
-        <v>33</v>
-      </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B25">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
-        <v>12345</v>
-      </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B28">
-        <v>1111</v>
-      </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B29">
-        <v>1234</v>
-      </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
-        <v>98765432</v>
-      </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1305,91 +1346,287 @@
       <c r="A34" t="s">
         <v>25</v>
       </c>
-      <c r="B34" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
         <v>91</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36">
-        <v>456776543456</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>96</v>
-      </c>
-      <c r="B38">
-        <v>876543456</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="B39">
-        <v>12345</v>
-      </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>34</v>
       </c>
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>48</v>
       </c>
       <c r="B42">
-        <v>212</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B37" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{5E462DF2-9605-47E9-8E3A-545A40285F5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA6CE37-2F51-4F04-BE43-03440191D4AE}">
+  <dimension ref="E1:E43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="51.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="5:5">
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="5:5">
+      <c r="E2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="5:5">
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="5:5">
+      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="5:5">
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="5:5">
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5">
+      <c r="E9" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="5:5">
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5">
+      <c r="E13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="5:5">
+      <c r="E15" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="5:5">
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="28" spans="5:5">
+      <c r="E28">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="29" spans="5:5">
+      <c r="E29">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="30" spans="5:5">
+      <c r="E30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="5:5">
+      <c r="E31">
+        <v>98765432</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5">
+      <c r="E32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5">
+      <c r="E35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36">
+        <v>456776543456</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38">
+        <v>876543456</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5">
+      <c r="E40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5">
+      <c r="E41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5">
+      <c r="E42">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="43" spans="5:5">
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E37" r:id="rId1" xr:uid="{25605B1F-87E3-4D9C-B83D-89E877D3F8E5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="16.140625" defaultRowHeight="15"/>
@@ -1693,4 +1930,323 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEDD8D6-745D-47C8-8F58-AE494657F5AE}">
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{6E76510B-36AA-40DF-A4B9-3BB4FF90A683}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Utilities/TestData/Customer.xlsx
+++ b/Utilities/TestData/Customer.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30318"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8FEB768-E3F2-41AF-B5AB-096944049A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB09F9B5-2168-4558-97D3-E7E4DBB1CE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="120">
   <si>
     <t>FieldName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Customer Name</t>
   </si>
   <si>
-    <t>asis</t>
+    <t>jemission</t>
   </si>
   <si>
     <t>First Name</t>
@@ -390,6 +390,12 @@
   </si>
   <si>
     <t>test comments</t>
+  </si>
+  <si>
+    <t>naimar</t>
+  </si>
+  <si>
+    <t>hanvi</t>
   </si>
 </sst>
 </file>
@@ -1409,14 +1415,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B37" r:id="rId1" xr:uid="{5E462DF2-9605-47E9-8E3A-545A40285F5A}"/>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA6CE37-2F51-4F04-BE43-03440191D4AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="E1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1620,14 +1626,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E37" r:id="rId1" xr:uid="{25605B1F-87E3-4D9C-B83D-89E877D3F8E5}"/>
+    <hyperlink ref="E37" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="16.140625" defaultRowHeight="15"/>
   <sheetData>
@@ -1678,7 +1684,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1686,7 +1692,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1705,7 +1711,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="30">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1933,7 +1939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEDD8D6-745D-47C8-8F58-AE494657F5AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2245,7 +2251,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B37" r:id="rId1" xr:uid="{6E76510B-36AA-40DF-A4B9-3BB4FF90A683}"/>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
